--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7014C7B-D812-43C9-AAAA-86A697976643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB264E0E59D4B36B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C276562-4067-4B37-8BAA-CBF3AACAC0A4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 14-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB264E0E59D4B36B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C276562-4067-4B37-8BAA-CBF3AACAC0A4}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB26CA4E9DD2236B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57068116-5560-49DB-8ABB-C4F2A80B042A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB26CA4E9DD2236B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57068116-5560-49DB-8ABB-C4F2A80B042A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218A417A-E234-40EE-97FB-3AB57EF8B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218A417A-E234-40EE-97FB-3AB57EF8B579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE584D36-3F95-482F-8777-4FE4F505412F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 14-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 17-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE584D36-3F95-482F-8777-4FE4F505412F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EB06E9-6051-413A-99BB-44A081A0AFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EB06E9-6051-413A-99BB-44A081A0AFF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB268D5E9FE97F6B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A308BBE-F636-4E98-883B-F4E281847572}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 17-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 18-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB268D5E9FE97F6B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A308BBE-F636-4E98-883B-F4E281847572}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB26AE36DAD6876B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85C89F2-270D-4D1B-B082-D1172D8E14B2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 18-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 21-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB26AE36DAD6876B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B85C89F2-270D-4D1B-B082-D1172D8E14B2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82A4591-A639-4E86-B97C-44546C255B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C82A4591-A639-4E86-B97C-44546C255B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768B5980-86B3-4DB0-9B6E-0B6421F58E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 21-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 22-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768B5980-86B3-4DB0-9B6E-0B6421F58E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685DA1BB-2239-4B12-A1D1-E8499144D678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685DA1BB-2239-4B12-A1D1-E8499144D678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2F1A39-B784-4CBB-9358-167CE061EACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 22-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 23-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2F1A39-B784-4CBB-9358-167CE061EACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB2692BE5BD10F6B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9458E94C-E397-4AB9-96FF-2D710A14E6B6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB2692BE5BD10F6B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9458E94C-E397-4AB9-96FF-2D710A14E6B6}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB262A2E1BFAA96B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B093330-CF4F-4E2A-94A7-EB4FEE25D848}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 23-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 24-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB262A2E1BFAA96B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B093330-CF4F-4E2A-94A7-EB4FEE25D848}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB262B561BEF496A664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7E12F4F-DE3E-44E9-9412-95690F5DF08F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB262B561BEF496A664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7E12F4F-DE3E-44E9-9412-95690F5DF08F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A7C162-40B1-4D21-A4A4-5EC7667B83B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 24-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 28-09-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A7C162-40B1-4D21-A4A4-5EC7667B83B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB260BE6D9D5096B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2A63DC-3B61-42C0-8E4A-2BFA169FB866}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 28-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-10-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685DA1BB-2239-4B12-A1D1-E8499144D678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E03EF3-BC1D-477A-9BF3-C0AC69FD81EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 22-09-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 07-10-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB260BE6D9D5096B664CCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A2A63DC-3B61-42C0-8E4A-2BFA169FB866}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C896EB1-1EBF-4523-A37D-549F5A82F0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 02-10-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 07-10-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -428,9 +428,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,7 +447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -464,7 +464,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -481,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -498,7 +498,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -515,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -532,7 +532,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -549,7 +549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -566,7 +566,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -600,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C896EB1-1EBF-4523-A37D-549F5A82F0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB26EDD65CFFE56A664CCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CC8B97-8E83-4F83-9823-DB362ABD7E61}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 07-10-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 08-10-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB26EDD65CFFE56A664CCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89CC8B97-8E83-4F83-9823-DB362ABD7E61}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAA336E-9F5F-416D-AECC-6AA680122BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 08-10-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-10-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAA336E-9F5F-416D-AECC-6AA680122BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4F96AA-6EE6-4F7E-94A4-A71A5D683C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Socialfaglige systemer_excel.XLSX
+++ b/html/Socialfaglige systemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4F96AA-6EE6-4F7E-94A4-A71A5D683C89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_A52A79AB48E5B990C9AB26F01619EDE56A664CCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{032627BF-637A-436C-99D3-0251DAE0C47D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Socialfaglige_systemer">'Opdateret d. 09-10-2026'!$A$1:$E$11</definedName>
+    <definedName name="Socialfaglige_systemer">'Opdateret d. 23-10-2026'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
